--- a/Documents/Translation_table.xlsx
+++ b/Documents/Translation_table.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\j0814240\Documents\F-C\Git\FlexChroma\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{993CD20C-BD8E-4CEA-810D-94134553E543}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C139D041-ABFE-431F-8A4B-FE6A94A61D0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6C5974D6-26C4-46D6-B546-EB46F1516DF4}"/>
   </bookViews>
@@ -36,16 +36,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="68">
   <si>
     <t>English</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>日本語</t>
-    <rPh sb="0" eb="3">
-      <t>ニホンゴ</t>
-    </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -334,17 +327,20 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>Contributors : English Translation by Sheepycloud</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>寄稿者：オリジナルサイト作成　Sheepycloud</t>
-    <rPh sb="0" eb="3">
-      <t>キコウシャ</t>
-    </rPh>
-    <rPh sb="12" eb="14">
-      <t>サクセイ</t>
-    </rPh>
+    <t>-</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Please suggest a natural German heading for this section.
+Examples:
+- Contributors
+- Credits
+- Acknowledgements
+Feel free to choose the most natural wording.</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Japanese</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1064,7 +1060,7 @@
     <row r="2" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A2" s="4"/>
       <c r="B2" s="7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C2" s="5"/>
       <c r="D2" s="6"/>
@@ -1086,22 +1082,22 @@
     <row r="4" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A4" s="4"/>
       <c r="B4" s="8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D4" s="10" t="s">
         <v>0</v>
       </c>
       <c r="E4" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="F4" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="F4" s="10" t="s">
-        <v>2</v>
-      </c>
       <c r="G4" s="11" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="H4" s="4"/>
     </row>
@@ -1111,17 +1107,17 @@
         <v>1</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D5" s="14" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E5" s="14" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F5" s="14"/>
       <c r="G5" s="15" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="H5" s="4"/>
     </row>
@@ -1131,13 +1127,13 @@
         <v>1</v>
       </c>
       <c r="C6" s="17" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D6" s="18" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E6" s="19" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F6" s="18"/>
       <c r="G6" s="20"/>
@@ -1149,13 +1145,13 @@
         <v>1</v>
       </c>
       <c r="C7" s="17" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D7" s="18" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E7" s="18" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F7" s="18"/>
       <c r="G7" s="20"/>
@@ -1167,13 +1163,13 @@
         <v>1</v>
       </c>
       <c r="C8" s="17" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D8" s="18" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E8" s="18" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F8" s="18"/>
       <c r="G8" s="20"/>
@@ -1185,13 +1181,13 @@
         <v>1</v>
       </c>
       <c r="C9" s="22" t="s">
+        <v>10</v>
+      </c>
+      <c r="D9" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="D9" s="23" t="s">
-        <v>12</v>
-      </c>
       <c r="E9" s="23" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F9" s="23"/>
       <c r="G9" s="24"/>
@@ -1203,13 +1199,13 @@
         <v>2</v>
       </c>
       <c r="C10" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D10" s="14" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E10" s="14" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F10" s="14"/>
       <c r="G10" s="15"/>
@@ -1221,13 +1217,13 @@
         <v>2</v>
       </c>
       <c r="C11" s="17" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D11" s="18" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E11" s="18" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F11" s="18"/>
       <c r="G11" s="20"/>
@@ -1239,13 +1235,13 @@
         <v>2</v>
       </c>
       <c r="C12" s="17" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D12" s="18" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E12" s="18" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F12" s="18"/>
       <c r="G12" s="20"/>
@@ -1257,13 +1253,13 @@
         <v>2</v>
       </c>
       <c r="C13" s="22" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D13" s="23" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E13" s="23" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F13" s="23"/>
       <c r="G13" s="24"/>
@@ -1275,13 +1271,13 @@
         <v>3</v>
       </c>
       <c r="C14" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D14" s="14" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E14" s="14" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F14" s="14"/>
       <c r="G14" s="15"/>
@@ -1293,13 +1289,13 @@
         <v>3</v>
       </c>
       <c r="C15" s="17" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D15" s="18" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E15" s="18" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F15" s="18"/>
       <c r="G15" s="20"/>
@@ -1311,13 +1307,13 @@
         <v>3</v>
       </c>
       <c r="C16" s="17" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D16" s="18" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E16" s="18" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F16" s="18"/>
       <c r="G16" s="20"/>
@@ -1329,13 +1325,13 @@
         <v>3</v>
       </c>
       <c r="C17" s="22" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D17" s="23" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E17" s="23" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F17" s="23"/>
       <c r="G17" s="24"/>
@@ -1347,13 +1343,13 @@
         <v>4</v>
       </c>
       <c r="C18" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D18" s="14" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E18" s="14" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F18" s="14"/>
       <c r="G18" s="15"/>
@@ -1365,13 +1361,13 @@
         <v>4</v>
       </c>
       <c r="C19" s="22" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D19" s="23" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E19" s="23" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F19" s="23"/>
       <c r="G19" s="24"/>
@@ -1383,13 +1379,13 @@
         <v>5</v>
       </c>
       <c r="C20" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D20" s="14" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E20" s="14" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F20" s="14"/>
       <c r="G20" s="15"/>
@@ -1401,13 +1397,13 @@
         <v>5</v>
       </c>
       <c r="C21" s="17" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D21" s="18" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E21" s="18" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F21" s="18"/>
       <c r="G21" s="20"/>
@@ -1419,13 +1415,13 @@
         <v>5</v>
       </c>
       <c r="C22" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="D22" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="D22" s="18" t="s">
-        <v>27</v>
-      </c>
       <c r="E22" s="18" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F22" s="18"/>
       <c r="G22" s="20"/>
@@ -1437,13 +1433,13 @@
         <v>5</v>
       </c>
       <c r="C23" s="17" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D23" s="18" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E23" s="18" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F23" s="18"/>
       <c r="G23" s="20"/>
@@ -1455,13 +1451,13 @@
         <v>5</v>
       </c>
       <c r="C24" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="D24" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="E24" s="18" t="s">
         <v>29</v>
-      </c>
-      <c r="D24" s="18" t="s">
-        <v>50</v>
-      </c>
-      <c r="E24" s="18" t="s">
-        <v>30</v>
       </c>
       <c r="F24" s="18"/>
       <c r="G24" s="20"/>
@@ -1473,13 +1469,13 @@
         <v>5</v>
       </c>
       <c r="C25" s="22" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D25" s="23" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E25" s="23" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F25" s="23"/>
       <c r="G25" s="24"/>
@@ -1491,13 +1487,13 @@
         <v>6</v>
       </c>
       <c r="C26" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D26" s="14" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E26" s="14" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F26" s="14"/>
       <c r="G26" s="15"/>
@@ -1509,13 +1505,13 @@
         <v>6</v>
       </c>
       <c r="C27" s="17" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D27" s="18" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E27" s="18" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F27" s="18"/>
       <c r="G27" s="20"/>
@@ -1527,13 +1523,13 @@
         <v>6</v>
       </c>
       <c r="C28" s="22" t="s">
+        <v>10</v>
+      </c>
+      <c r="D28" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="D28" s="23" t="s">
-        <v>12</v>
-      </c>
       <c r="E28" s="23" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F28" s="23"/>
       <c r="G28" s="24"/>
@@ -1545,13 +1541,13 @@
         <v>7</v>
       </c>
       <c r="C29" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D29" s="14" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E29" s="14" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F29" s="14"/>
       <c r="G29" s="15"/>
@@ -1563,13 +1559,13 @@
         <v>7</v>
       </c>
       <c r="C30" s="17" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D30" s="18" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E30" s="18" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F30" s="18"/>
       <c r="G30" s="20"/>
@@ -1581,13 +1577,13 @@
         <v>7</v>
       </c>
       <c r="C31" s="22" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D31" s="23" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E31" s="23" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F31" s="23"/>
       <c r="G31" s="24"/>
@@ -1599,13 +1595,13 @@
         <v>8</v>
       </c>
       <c r="C32" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D32" s="14" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E32" s="14" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F32" s="14"/>
       <c r="G32" s="15"/>
@@ -1617,13 +1613,13 @@
         <v>8</v>
       </c>
       <c r="C33" s="22" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D33" s="23" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E33" s="23" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F33" s="23"/>
       <c r="G33" s="24"/>
@@ -1635,13 +1631,13 @@
         <v>9</v>
       </c>
       <c r="C34" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D34" s="14" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E34" s="14" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F34" s="14"/>
       <c r="G34" s="15"/>
@@ -1653,13 +1649,13 @@
         <v>9</v>
       </c>
       <c r="C35" s="22" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D35" s="23" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E35" s="23" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F35" s="23"/>
       <c r="G35" s="24"/>
@@ -1671,13 +1667,13 @@
         <v>10</v>
       </c>
       <c r="C36" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D36" s="14" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E36" s="14" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F36" s="14"/>
       <c r="G36" s="15"/>
@@ -1689,33 +1685,35 @@
         <v>10</v>
       </c>
       <c r="C37" s="26" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D37" s="27" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E37" s="27" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F37" s="27"/>
       <c r="G37" s="28"/>
       <c r="H37" s="4"/>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:8" ht="115.5" x14ac:dyDescent="0.4">
       <c r="A38" s="4"/>
       <c r="B38" s="21">
         <v>10</v>
       </c>
       <c r="C38" s="22" t="s">
+        <v>64</v>
+      </c>
+      <c r="D38" s="29" t="s">
         <v>65</v>
       </c>
-      <c r="D38" s="29" t="s">
+      <c r="E38" s="29" t="s">
+        <v>65</v>
+      </c>
+      <c r="F38" s="29" t="s">
         <v>66</v>
       </c>
-      <c r="E38" s="29" t="s">
-        <v>67</v>
-      </c>
-      <c r="F38" s="29"/>
       <c r="G38" s="24"/>
       <c r="H38" s="4"/>
     </row>

--- a/Documents/Translation_table.xlsx
+++ b/Documents/Translation_table.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\j0814240\Documents\F-C\Git\FlexChroma\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA9E491D-491A-4463-A89E-72B8265001C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2D65D98-4F84-4C66-A500-F8478538B402}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="4605" windowWidth="21450" windowHeight="13110" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7740" yWindow="-13500" windowWidth="19095" windowHeight="12555" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Portal" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="140">
   <si>
     <t>Portal Site Translation Table</t>
   </si>
@@ -388,185 +388,197 @@
   </si>
   <si>
     <t>Mehr als Standard-Filamentfarben.</t>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>Drucke die Farben deiner Fantasie.</t>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>Bibliothek</t>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>FlexChroma Hub/Zentrum</t>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>Library</t>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>Back to Portal</t>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>FlexChroma Tour Guide</t>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>Learn how to navigate FlexChroma and choose the right Series and Model.</t>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>Brim Information Guide</t>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>Blend Filament Guide</t>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>Learn how to create custom filament colors by blending two filaments.</t>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>Blend Color Checker Guide</t>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>Gradient Filament Guide</t>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>Learn how to design smooth color transitions along filament length.</t>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>Under Construction</t>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>notice</t>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>Blend Color Chart</t>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>Browse measured filament colors and find reference color data.</t>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>PLA Basic - Basic Set</t>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>I will keep a record of my thoughts on the development process, measured color data, and tips for using FlexChroma effectively.</t>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>About</t>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>Contributors</t>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>-</t>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>Link name</t>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>PLA Basic - Monotone Set</t>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>PLA Matte - Semi-Basic Set</t>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>PLA Matte - Pastel Set</t>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>PLA Silk+ - Metaric Set</t>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>PLA Translucent - Semi-Basic Set</t>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>PETG Basic - Semi-Basic Set</t>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>FlexChroma Document Repository</t>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>FlexChroma 資料書庫</t>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>Portal へ戻る</t>
     <rPh sb="8" eb="9">
       <t>モド</t>
     </rPh>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>FlexChromaの閲覧方法や、適切なシリーズやモデルの選び方についてご説明します。</t>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>ブリムの情報からにフィラメントの仕様を読み解きましょう。</t>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>Let's analyze the filament specifications based on the information from Brim.</t>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>2種類のフィラメントを混ぜ合わせて、オリジナルのフィラメントカラーを作る方法をご紹介します。</t>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>最適な色の組み合わせを見つけるために、少ないフィラメントで多彩な混色結果を一度に確認しましょう。</t>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>Find the perfect color combination by comparing a wide range of mixing results at once, using only a small amount of filament.</t>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>フィラメントの長さに沿って滑らかな色のグラデーションをデザインする方法を学びましょう。</t>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>測定済みの混色フィラメントの色を集めました、代表的な混色結果はこちらから確認いただけます。</t>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>私は記録していきます - 開発プロセスに関する考察、測定した色データ、そしてFlexChromaを効果的に活用するためのヒント</t>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Paragraph description</t>
+    <phoneticPr fontId="2"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <charset val="128"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -589,6 +601,13 @@
       <name val="IBM Plex Sans JP"/>
       <family val="3"/>
       <charset val="128"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -874,115 +893,121 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="3">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="標準 2" xfId="1" xr:uid="{F88D72C2-C36C-4A89-891F-94EE9B6D17CC}"/>
+    <cellStyle name="標準 3" xfId="2" xr:uid="{B83318FC-0288-46BB-BB96-45ABEB6914B9}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -29570,7 +29595,7 @@
       <c r="Z1000" s="4"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="1"/>
+  <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
 </worksheet>
@@ -29582,7 +29607,7 @@
   <sheetFormatPr defaultColWidth="12.7109375" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2.85546875" style="5" customWidth="1"/>
-    <col min="2" max="2" width="8.28515625" style="5" customWidth="1"/>
+    <col min="2" max="2" width="10.42578125" style="5" customWidth="1"/>
     <col min="3" max="3" width="21.5703125" style="5" bestFit="1" customWidth="1"/>
     <col min="4" max="7" width="43.28515625" style="5" customWidth="1"/>
     <col min="8" max="8" width="2.7109375" style="5" customWidth="1"/>
@@ -30012,7 +30037,7 @@
         <v>4</v>
       </c>
       <c r="C13" s="20" t="s">
-        <v>22</v>
+        <v>139</v>
       </c>
       <c r="D13" s="21" t="s">
         <v>107</v>
@@ -57629,7 +57654,7 @@
       <c r="Z993" s="4"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="1"/>
+  <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
 </worksheet>

--- a/Documents/Translation_table.xlsx
+++ b/Documents/Translation_table.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\j0814240\Documents\F-C\Git\FlexChroma\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2D65D98-4F84-4C66-A500-F8478538B402}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF690AAE-4F9F-4033-82F3-16A7A7A445CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7740" yWindow="-13500" windowWidth="19095" windowHeight="12555" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3795" yWindow="4845" windowWidth="19095" windowHeight="12360" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Portal" sheetId="1" r:id="rId1"/>

--- a/Documents/Translation_table.xlsx
+++ b/Documents/Translation_table.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\j0814240\Documents\F-C\Git\FlexChroma\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF690AAE-4F9F-4033-82F3-16A7A7A445CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D629BB97-E83F-43B5-AD36-2B2FD300A63A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3795" yWindow="4845" windowWidth="19095" windowHeight="12360" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="90" yWindow="7395" windowWidth="19095" windowHeight="12360" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Portal" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="143">
   <si>
     <t>Portal Site Translation Table</t>
   </si>
@@ -561,6 +561,18 @@
     <t>Paragraph description</t>
     <phoneticPr fontId="2"/>
   </si>
+  <si>
+    <t>Site description</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>FlexChromaプロジェクトの公式ポータルサイト</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>The official portal for the FlexChroma project.</t>
+    <phoneticPr fontId="2"/>
+  </si>
 </sst>
 </file>
 
@@ -624,7 +636,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="21">
+  <borders count="23">
     <border>
       <left/>
       <right/>
@@ -892,6 +904,30 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="hair">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="hair">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="hair">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -900,7 +936,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1001,6 +1037,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1220,7 +1265,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Z1000"/>
+  <dimension ref="A1:Z1001"/>
   <sheetFormatPr defaultColWidth="12.7109375" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2.85546875" style="5" customWidth="1"/>
@@ -1396,24 +1441,22 @@
       <c r="Y5" s="4"/>
       <c r="Z5" s="4"/>
     </row>
-    <row r="6" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:26" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
-      <c r="B6" s="15">
+      <c r="B6" s="34">
         <v>1</v>
       </c>
-      <c r="C6" s="16" t="s">
-        <v>9</v>
+      <c r="C6" s="35" t="s">
+        <v>140</v>
       </c>
-      <c r="D6" s="17" t="s">
-        <v>10</v>
+      <c r="D6" s="36" t="s">
+        <v>142</v>
       </c>
-      <c r="E6" s="17" t="s">
-        <v>11</v>
+      <c r="E6" s="36" t="s">
+        <v>141</v>
       </c>
-      <c r="F6" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="G6" s="18"/>
+      <c r="F6" s="17"/>
+      <c r="G6" s="26"/>
       <c r="H6" s="1"/>
       <c r="I6" s="4"/>
       <c r="J6" s="4"/>
@@ -1434,22 +1477,22 @@
       <c r="Y6" s="4"/>
       <c r="Z6" s="4"/>
     </row>
-    <row r="7" spans="1:26" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
       <c r="B7" s="15">
         <v>1</v>
       </c>
       <c r="C7" s="16" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D7" s="17" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E7" s="17" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G7" s="18"/>
       <c r="H7" s="1"/>
@@ -1478,20 +1521,18 @@
         <v>1</v>
       </c>
       <c r="C8" s="16" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D8" s="17" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E8" s="17" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
-      <c r="F8" s="17" t="s">
-        <v>100</v>
+      <c r="F8" s="4" t="s">
+        <v>98</v>
       </c>
-      <c r="G8" s="18" t="s">
-        <v>16</v>
-      </c>
+      <c r="G8" s="18"/>
       <c r="H8" s="1"/>
       <c r="I8" s="4"/>
       <c r="J8" s="4"/>
@@ -1514,22 +1555,24 @@
     </row>
     <row r="9" spans="1:26" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1"/>
-      <c r="B9" s="19">
+      <c r="B9" s="15">
         <v>1</v>
       </c>
-      <c r="C9" s="20" t="s">
+      <c r="C9" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="D9" s="21" t="s">
-        <v>17</v>
+      <c r="D9" s="17" t="s">
+        <v>15</v>
       </c>
-      <c r="E9" s="21" t="s">
-        <v>17</v>
+      <c r="E9" s="17" t="s">
+        <v>15</v>
       </c>
-      <c r="F9" s="4" t="s">
-        <v>99</v>
+      <c r="F9" s="17" t="s">
+        <v>100</v>
       </c>
-      <c r="G9" s="22"/>
+      <c r="G9" s="18" t="s">
+        <v>16</v>
+      </c>
       <c r="H9" s="1"/>
       <c r="I9" s="4"/>
       <c r="J9" s="4"/>
@@ -1552,22 +1595,22 @@
     </row>
     <row r="10" spans="1:26" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1"/>
-      <c r="B10" s="11">
-        <v>2</v>
+      <c r="B10" s="19">
+        <v>1</v>
       </c>
-      <c r="C10" s="12" t="s">
-        <v>19</v>
+      <c r="C10" s="20" t="s">
+        <v>14</v>
       </c>
-      <c r="D10" s="13" t="s">
-        <v>20</v>
+      <c r="D10" s="21" t="s">
+        <v>17</v>
       </c>
-      <c r="E10" s="13" t="s">
-        <v>20</v>
+      <c r="E10" s="21" t="s">
+        <v>17</v>
       </c>
-      <c r="F10" s="13" t="s">
-        <v>21</v>
+      <c r="F10" s="4" t="s">
+        <v>99</v>
       </c>
-      <c r="G10" s="14"/>
+      <c r="G10" s="22"/>
       <c r="H10" s="1"/>
       <c r="I10" s="4"/>
       <c r="J10" s="4"/>
@@ -1588,24 +1631,24 @@
       <c r="Y10" s="4"/>
       <c r="Z10" s="4"/>
     </row>
-    <row r="11" spans="1:26" ht="66" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:26" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1"/>
-      <c r="B11" s="15">
+      <c r="B11" s="11">
         <v>2</v>
       </c>
-      <c r="C11" s="16" t="s">
-        <v>22</v>
+      <c r="C11" s="12" t="s">
+        <v>19</v>
       </c>
-      <c r="D11" s="17" t="s">
-        <v>23</v>
+      <c r="D11" s="13" t="s">
+        <v>20</v>
       </c>
-      <c r="E11" s="17" t="s">
-        <v>24</v>
+      <c r="E11" s="13" t="s">
+        <v>20</v>
       </c>
-      <c r="F11" s="30" t="s">
-        <v>25</v>
+      <c r="F11" s="13" t="s">
+        <v>21</v>
       </c>
-      <c r="G11" s="18"/>
+      <c r="G11" s="14"/>
       <c r="H11" s="1"/>
       <c r="I11" s="4"/>
       <c r="J11" s="4"/>
@@ -1626,22 +1669,22 @@
       <c r="Y11" s="4"/>
       <c r="Z11" s="4"/>
     </row>
-    <row r="12" spans="1:26" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:26" ht="66" x14ac:dyDescent="0.25">
       <c r="A12" s="1"/>
       <c r="B12" s="15">
         <v>2</v>
       </c>
       <c r="C12" s="16" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="D12" s="17" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E12" s="17" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
-      <c r="F12" s="17" t="s">
-        <v>27</v>
+      <c r="F12" s="30" t="s">
+        <v>25</v>
       </c>
       <c r="G12" s="18"/>
       <c r="H12" s="1"/>
@@ -1666,22 +1709,22 @@
     </row>
     <row r="13" spans="1:26" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1"/>
-      <c r="B13" s="19">
+      <c r="B13" s="15">
         <v>2</v>
       </c>
-      <c r="C13" s="20" t="s">
+      <c r="C13" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="D13" s="21" t="s">
-        <v>28</v>
+      <c r="D13" s="17" t="s">
+        <v>26</v>
       </c>
-      <c r="E13" s="21" t="s">
-        <v>28</v>
+      <c r="E13" s="17" t="s">
+        <v>26</v>
       </c>
-      <c r="F13" s="4" t="s">
-        <v>29</v>
+      <c r="F13" s="17" t="s">
+        <v>27</v>
       </c>
-      <c r="G13" s="22"/>
+      <c r="G13" s="18"/>
       <c r="H13" s="1"/>
       <c r="I13" s="4"/>
       <c r="J13" s="4"/>
@@ -1704,22 +1747,22 @@
     </row>
     <row r="14" spans="1:26" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1"/>
-      <c r="B14" s="11">
-        <v>3</v>
+      <c r="B14" s="19">
+        <v>2</v>
       </c>
-      <c r="C14" s="12" t="s">
-        <v>19</v>
+      <c r="C14" s="20" t="s">
+        <v>14</v>
       </c>
-      <c r="D14" s="13" t="s">
-        <v>30</v>
+      <c r="D14" s="21" t="s">
+        <v>28</v>
       </c>
-      <c r="E14" s="13" t="s">
-        <v>30</v>
+      <c r="E14" s="21" t="s">
+        <v>28</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
-      <c r="G14" s="14"/>
+      <c r="G14" s="22"/>
       <c r="H14" s="1"/>
       <c r="I14" s="4"/>
       <c r="J14" s="4"/>
@@ -1740,24 +1783,24 @@
       <c r="Y14" s="4"/>
       <c r="Z14" s="4"/>
     </row>
-    <row r="15" spans="1:26" ht="115.5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:26" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1"/>
-      <c r="B15" s="15">
+      <c r="B15" s="11">
         <v>3</v>
       </c>
-      <c r="C15" s="16" t="s">
-        <v>22</v>
+      <c r="C15" s="12" t="s">
+        <v>19</v>
       </c>
-      <c r="D15" s="17" t="s">
-        <v>32</v>
+      <c r="D15" s="13" t="s">
+        <v>30</v>
       </c>
-      <c r="E15" s="17" t="s">
-        <v>33</v>
+      <c r="E15" s="13" t="s">
+        <v>30</v>
       </c>
-      <c r="F15" s="17" t="s">
-        <v>34</v>
+      <c r="F15" s="4" t="s">
+        <v>31</v>
       </c>
-      <c r="G15" s="18"/>
+      <c r="G15" s="14"/>
       <c r="H15" s="1"/>
       <c r="I15" s="4"/>
       <c r="J15" s="4"/>
@@ -1778,22 +1821,22 @@
       <c r="Y15" s="4"/>
       <c r="Z15" s="4"/>
     </row>
-    <row r="16" spans="1:26" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:26" ht="115.5" x14ac:dyDescent="0.25">
       <c r="A16" s="1"/>
       <c r="B16" s="15">
         <v>3</v>
       </c>
       <c r="C16" s="16" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="D16" s="17" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="E16" s="17" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
-      <c r="F16" s="4" t="s">
-        <v>36</v>
+      <c r="F16" s="17" t="s">
+        <v>34</v>
       </c>
       <c r="G16" s="18"/>
       <c r="H16" s="1"/>
@@ -1818,22 +1861,22 @@
     </row>
     <row r="17" spans="1:26" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="1"/>
-      <c r="B17" s="19">
+      <c r="B17" s="15">
         <v>3</v>
       </c>
-      <c r="C17" s="20" t="s">
+      <c r="C17" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="D17" s="21" t="s">
-        <v>37</v>
+      <c r="D17" s="17" t="s">
+        <v>35</v>
       </c>
-      <c r="E17" s="21" t="s">
-        <v>37</v>
+      <c r="E17" s="17" t="s">
+        <v>35</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
-      <c r="G17" s="22"/>
+      <c r="G17" s="18"/>
       <c r="H17" s="1"/>
       <c r="I17" s="4"/>
       <c r="J17" s="4"/>
@@ -1856,22 +1899,22 @@
     </row>
     <row r="18" spans="1:26" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="1"/>
-      <c r="B18" s="11">
-        <v>4</v>
+      <c r="B18" s="19">
+        <v>3</v>
       </c>
-      <c r="C18" s="12" t="s">
-        <v>19</v>
+      <c r="C18" s="20" t="s">
+        <v>14</v>
       </c>
-      <c r="D18" s="13" t="s">
-        <v>39</v>
+      <c r="D18" s="21" t="s">
+        <v>37</v>
       </c>
-      <c r="E18" s="13" t="s">
-        <v>40</v>
+      <c r="E18" s="21" t="s">
+        <v>37</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
-      <c r="G18" s="14"/>
+      <c r="G18" s="22"/>
       <c r="H18" s="1"/>
       <c r="I18" s="4"/>
       <c r="J18" s="4"/>
@@ -1892,24 +1935,24 @@
       <c r="Y18" s="4"/>
       <c r="Z18" s="4"/>
     </row>
-    <row r="19" spans="1:26" ht="99" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:26" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="1"/>
-      <c r="B19" s="19">
+      <c r="B19" s="11">
         <v>4</v>
       </c>
-      <c r="C19" s="20" t="s">
-        <v>22</v>
+      <c r="C19" s="12" t="s">
+        <v>19</v>
       </c>
-      <c r="D19" s="21" t="s">
-        <v>42</v>
+      <c r="D19" s="13" t="s">
+        <v>39</v>
       </c>
-      <c r="E19" s="21" t="s">
-        <v>43</v>
+      <c r="E19" s="13" t="s">
+        <v>40</v>
       </c>
-      <c r="F19" s="21" t="s">
-        <v>44</v>
+      <c r="F19" s="4" t="s">
+        <v>41</v>
       </c>
-      <c r="G19" s="22"/>
+      <c r="G19" s="14"/>
       <c r="H19" s="1"/>
       <c r="I19" s="4"/>
       <c r="J19" s="4"/>
@@ -1930,24 +1973,24 @@
       <c r="Y19" s="4"/>
       <c r="Z19" s="4"/>
     </row>
-    <row r="20" spans="1:26" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:26" ht="99" x14ac:dyDescent="0.25">
       <c r="A20" s="1"/>
-      <c r="B20" s="11">
-        <v>5</v>
+      <c r="B20" s="19">
+        <v>4</v>
       </c>
-      <c r="C20" s="12" t="s">
-        <v>19</v>
+      <c r="C20" s="20" t="s">
+        <v>22</v>
       </c>
-      <c r="D20" s="13" t="s">
-        <v>45</v>
+      <c r="D20" s="21" t="s">
+        <v>42</v>
       </c>
-      <c r="E20" s="13" t="s">
-        <v>46</v>
+      <c r="E20" s="21" t="s">
+        <v>43</v>
       </c>
-      <c r="F20" s="13" t="s">
-        <v>47</v>
+      <c r="F20" s="21" t="s">
+        <v>44</v>
       </c>
-      <c r="G20" s="14"/>
+      <c r="G20" s="22"/>
       <c r="H20" s="1"/>
       <c r="I20" s="4"/>
       <c r="J20" s="4"/>
@@ -1970,22 +2013,22 @@
     </row>
     <row r="21" spans="1:26" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="1"/>
-      <c r="B21" s="15">
+      <c r="B21" s="11">
         <v>5</v>
       </c>
-      <c r="C21" s="16" t="s">
-        <v>48</v>
+      <c r="C21" s="12" t="s">
+        <v>19</v>
       </c>
-      <c r="D21" s="17" t="s">
-        <v>49</v>
+      <c r="D21" s="13" t="s">
+        <v>45</v>
       </c>
-      <c r="E21" s="17" t="s">
-        <v>49</v>
+      <c r="E21" s="13" t="s">
+        <v>46</v>
       </c>
-      <c r="F21" s="17" t="s">
-        <v>50</v>
+      <c r="F21" s="13" t="s">
+        <v>47</v>
       </c>
-      <c r="G21" s="18"/>
+      <c r="G21" s="14"/>
       <c r="H21" s="1"/>
       <c r="I21" s="4"/>
       <c r="J21" s="4"/>
@@ -2015,13 +2058,13 @@
         <v>48</v>
       </c>
       <c r="D22" s="17" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E22" s="17" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F22" s="17" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="G22" s="18"/>
       <c r="H22" s="1"/>
@@ -2050,16 +2093,16 @@
         <v>5</v>
       </c>
       <c r="C23" s="16" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="D23" s="17" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E23" s="17" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
-      <c r="F23" s="4" t="s">
-        <v>56</v>
+      <c r="F23" s="17" t="s">
+        <v>52</v>
       </c>
       <c r="G23" s="18"/>
       <c r="H23" s="1"/>
@@ -2091,13 +2134,13 @@
         <v>53</v>
       </c>
       <c r="D24" s="17" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="E24" s="17" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
-      <c r="F24" s="17" t="s">
-        <v>59</v>
+      <c r="F24" s="4" t="s">
+        <v>56</v>
       </c>
       <c r="G24" s="18"/>
       <c r="H24" s="1"/>
@@ -2120,24 +2163,24 @@
       <c r="Y24" s="4"/>
       <c r="Z24" s="4"/>
     </row>
-    <row r="25" spans="1:26" ht="49.5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:26" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="1"/>
-      <c r="B25" s="19">
+      <c r="B25" s="15">
         <v>5</v>
       </c>
-      <c r="C25" s="20" t="s">
+      <c r="C25" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="D25" s="21" t="s">
-        <v>60</v>
+      <c r="D25" s="17" t="s">
+        <v>57</v>
       </c>
-      <c r="E25" s="21" t="s">
-        <v>61</v>
+      <c r="E25" s="17" t="s">
+        <v>58</v>
       </c>
-      <c r="F25" s="21" t="s">
-        <v>62</v>
+      <c r="F25" s="17" t="s">
+        <v>59</v>
       </c>
-      <c r="G25" s="22"/>
+      <c r="G25" s="18"/>
       <c r="H25" s="1"/>
       <c r="I25" s="4"/>
       <c r="J25" s="4"/>
@@ -2158,24 +2201,24 @@
       <c r="Y25" s="4"/>
       <c r="Z25" s="4"/>
     </row>
-    <row r="26" spans="1:26" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:26" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A26" s="1"/>
-      <c r="B26" s="11">
-        <v>6</v>
+      <c r="B26" s="19">
+        <v>5</v>
       </c>
-      <c r="C26" s="12" t="s">
-        <v>19</v>
+      <c r="C26" s="20" t="s">
+        <v>53</v>
       </c>
-      <c r="D26" s="13" t="s">
-        <v>17</v>
+      <c r="D26" s="21" t="s">
+        <v>60</v>
       </c>
-      <c r="E26" s="13" t="s">
-        <v>63</v>
+      <c r="E26" s="21" t="s">
+        <v>61</v>
       </c>
-      <c r="F26" s="4" t="s">
-        <v>18</v>
+      <c r="F26" s="21" t="s">
+        <v>62</v>
       </c>
-      <c r="G26" s="14"/>
+      <c r="G26" s="22"/>
       <c r="H26" s="1"/>
       <c r="I26" s="4"/>
       <c r="J26" s="4"/>
@@ -2196,24 +2239,24 @@
       <c r="Y26" s="4"/>
       <c r="Z26" s="4"/>
     </row>
-    <row r="27" spans="1:26" ht="49.5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:26" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="1"/>
-      <c r="B27" s="15">
+      <c r="B27" s="11">
         <v>6</v>
       </c>
-      <c r="C27" s="16" t="s">
-        <v>22</v>
+      <c r="C27" s="12" t="s">
+        <v>19</v>
       </c>
-      <c r="D27" s="17" t="s">
-        <v>64</v>
+      <c r="D27" s="13" t="s">
+        <v>17</v>
       </c>
-      <c r="E27" s="17" t="s">
-        <v>65</v>
+      <c r="E27" s="13" t="s">
+        <v>63</v>
       </c>
-      <c r="F27" s="17" t="s">
-        <v>66</v>
+      <c r="F27" s="4" t="s">
+        <v>18</v>
       </c>
-      <c r="G27" s="18"/>
+      <c r="G27" s="14"/>
       <c r="H27" s="1"/>
       <c r="I27" s="4"/>
       <c r="J27" s="4"/>
@@ -2234,24 +2277,24 @@
       <c r="Y27" s="4"/>
       <c r="Z27" s="4"/>
     </row>
-    <row r="28" spans="1:26" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:26" ht="49.5" x14ac:dyDescent="0.25">
       <c r="A28" s="1"/>
-      <c r="B28" s="19">
+      <c r="B28" s="15">
         <v>6</v>
       </c>
-      <c r="C28" s="20" t="s">
-        <v>14</v>
+      <c r="C28" s="16" t="s">
+        <v>22</v>
       </c>
-      <c r="D28" s="21" t="s">
-        <v>17</v>
+      <c r="D28" s="17" t="s">
+        <v>64</v>
       </c>
-      <c r="E28" s="21" t="s">
-        <v>17</v>
+      <c r="E28" s="17" t="s">
+        <v>65</v>
       </c>
-      <c r="F28" s="4" t="s">
-        <v>18</v>
+      <c r="F28" s="17" t="s">
+        <v>66</v>
       </c>
-      <c r="G28" s="22"/>
+      <c r="G28" s="18"/>
       <c r="H28" s="1"/>
       <c r="I28" s="4"/>
       <c r="J28" s="4"/>
@@ -2274,22 +2317,22 @@
     </row>
     <row r="29" spans="1:26" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="1"/>
-      <c r="B29" s="11">
-        <v>7</v>
+      <c r="B29" s="19">
+        <v>6</v>
       </c>
-      <c r="C29" s="12" t="s">
-        <v>19</v>
+      <c r="C29" s="20" t="s">
+        <v>14</v>
       </c>
-      <c r="D29" s="13" t="s">
-        <v>67</v>
+      <c r="D29" s="21" t="s">
+        <v>17</v>
       </c>
-      <c r="E29" s="13" t="s">
-        <v>68</v>
+      <c r="E29" s="21" t="s">
+        <v>17</v>
       </c>
-      <c r="F29" s="5" t="s">
-        <v>69</v>
+      <c r="F29" s="4" t="s">
+        <v>18</v>
       </c>
-      <c r="G29" s="14"/>
+      <c r="G29" s="22"/>
       <c r="H29" s="1"/>
       <c r="I29" s="4"/>
       <c r="J29" s="4"/>
@@ -2310,24 +2353,24 @@
       <c r="Y29" s="4"/>
       <c r="Z29" s="4"/>
     </row>
-    <row r="30" spans="1:26" ht="115.5" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:26" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="1"/>
-      <c r="B30" s="15">
+      <c r="B30" s="11">
         <v>7</v>
       </c>
-      <c r="C30" s="16" t="s">
-        <v>22</v>
+      <c r="C30" s="12" t="s">
+        <v>19</v>
       </c>
-      <c r="D30" s="17" t="s">
-        <v>70</v>
+      <c r="D30" s="13" t="s">
+        <v>67</v>
       </c>
-      <c r="E30" s="17" t="s">
-        <v>71</v>
+      <c r="E30" s="13" t="s">
+        <v>68</v>
       </c>
-      <c r="F30" s="17" t="s">
-        <v>72</v>
+      <c r="F30" s="5" t="s">
+        <v>69</v>
       </c>
-      <c r="G30" s="18"/>
+      <c r="G30" s="14"/>
       <c r="H30" s="1"/>
       <c r="I30" s="4"/>
       <c r="J30" s="4"/>
@@ -2348,26 +2391,24 @@
       <c r="Y30" s="4"/>
       <c r="Z30" s="4"/>
     </row>
-    <row r="31" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:26" ht="115.5" x14ac:dyDescent="0.25">
       <c r="A31" s="1"/>
-      <c r="B31" s="19">
+      <c r="B31" s="15">
         <v>7</v>
       </c>
-      <c r="C31" s="20" t="s">
-        <v>14</v>
+      <c r="C31" s="16" t="s">
+        <v>22</v>
       </c>
-      <c r="D31" s="21" t="s">
-        <v>73</v>
+      <c r="D31" s="17" t="s">
+        <v>70</v>
       </c>
-      <c r="E31" s="21" t="s">
-        <v>73</v>
+      <c r="E31" s="17" t="s">
+        <v>71</v>
       </c>
-      <c r="F31" s="4" t="s">
-        <v>74</v>
+      <c r="F31" s="17" t="s">
+        <v>72</v>
       </c>
-      <c r="G31" s="22" t="s">
-        <v>75</v>
-      </c>
+      <c r="G31" s="18"/>
       <c r="H31" s="1"/>
       <c r="I31" s="4"/>
       <c r="J31" s="4"/>
@@ -2388,25 +2429,25 @@
       <c r="Y31" s="4"/>
       <c r="Z31" s="4"/>
     </row>
-    <row r="32" spans="1:26" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A32" s="1"/>
-      <c r="B32" s="11">
-        <v>8</v>
+      <c r="B32" s="19">
+        <v>7</v>
       </c>
-      <c r="C32" s="12" t="s">
-        <v>19</v>
+      <c r="C32" s="20" t="s">
+        <v>14</v>
       </c>
-      <c r="D32" s="13" t="s">
-        <v>76</v>
+      <c r="D32" s="21" t="s">
+        <v>73</v>
       </c>
-      <c r="E32" s="13" t="s">
-        <v>76</v>
+      <c r="E32" s="21" t="s">
+        <v>73</v>
       </c>
-      <c r="F32" s="13" t="s">
-        <v>76</v>
+      <c r="F32" s="4" t="s">
+        <v>74</v>
       </c>
-      <c r="G32" s="14" t="s">
-        <v>77</v>
+      <c r="G32" s="22" t="s">
+        <v>75</v>
       </c>
       <c r="H32" s="1"/>
       <c r="I32" s="4"/>
@@ -2428,24 +2469,26 @@
       <c r="Y32" s="4"/>
       <c r="Z32" s="4"/>
     </row>
-    <row r="33" spans="1:26" ht="264" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:26" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="1"/>
-      <c r="B33" s="19">
+      <c r="B33" s="11">
         <v>8</v>
       </c>
-      <c r="C33" s="20" t="s">
-        <v>22</v>
+      <c r="C33" s="12" t="s">
+        <v>19</v>
       </c>
-      <c r="D33" s="21" t="s">
-        <v>78</v>
+      <c r="D33" s="13" t="s">
+        <v>76</v>
       </c>
-      <c r="E33" s="21" t="s">
-        <v>79</v>
+      <c r="E33" s="13" t="s">
+        <v>76</v>
       </c>
-      <c r="F33" s="21" t="s">
-        <v>80</v>
+      <c r="F33" s="13" t="s">
+        <v>76</v>
       </c>
-      <c r="G33" s="22"/>
+      <c r="G33" s="14" t="s">
+        <v>77</v>
+      </c>
       <c r="H33" s="1"/>
       <c r="I33" s="4"/>
       <c r="J33" s="4"/>
@@ -2466,24 +2509,24 @@
       <c r="Y33" s="4"/>
       <c r="Z33" s="4"/>
     </row>
-    <row r="34" spans="1:26" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:26" ht="264" x14ac:dyDescent="0.25">
       <c r="A34" s="1"/>
-      <c r="B34" s="11">
-        <v>9</v>
+      <c r="B34" s="19">
+        <v>8</v>
       </c>
-      <c r="C34" s="12" t="s">
-        <v>19</v>
+      <c r="C34" s="20" t="s">
+        <v>22</v>
       </c>
-      <c r="D34" s="13" t="s">
-        <v>81</v>
+      <c r="D34" s="21" t="s">
+        <v>78</v>
       </c>
-      <c r="E34" s="13" t="s">
-        <v>82</v>
+      <c r="E34" s="21" t="s">
+        <v>79</v>
       </c>
-      <c r="F34" s="13" t="s">
-        <v>83</v>
+      <c r="F34" s="21" t="s">
+        <v>80</v>
       </c>
-      <c r="G34" s="14"/>
+      <c r="G34" s="22"/>
       <c r="H34" s="1"/>
       <c r="I34" s="4"/>
       <c r="J34" s="4"/>
@@ -2504,24 +2547,24 @@
       <c r="Y34" s="4"/>
       <c r="Z34" s="4"/>
     </row>
-    <row r="35" spans="1:26" ht="247.5" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:26" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="1"/>
-      <c r="B35" s="19">
+      <c r="B35" s="11">
         <v>9</v>
       </c>
-      <c r="C35" s="20" t="s">
-        <v>22</v>
+      <c r="C35" s="12" t="s">
+        <v>19</v>
       </c>
-      <c r="D35" s="21" t="s">
-        <v>84</v>
+      <c r="D35" s="13" t="s">
+        <v>81</v>
       </c>
-      <c r="E35" s="21" t="s">
-        <v>85</v>
+      <c r="E35" s="13" t="s">
+        <v>82</v>
       </c>
-      <c r="F35" s="21" t="s">
-        <v>86</v>
+      <c r="F35" s="13" t="s">
+        <v>83</v>
       </c>
-      <c r="G35" s="22"/>
+      <c r="G35" s="14"/>
       <c r="H35" s="1"/>
       <c r="I35" s="4"/>
       <c r="J35" s="4"/>
@@ -2542,24 +2585,24 @@
       <c r="Y35" s="4"/>
       <c r="Z35" s="4"/>
     </row>
-    <row r="36" spans="1:26" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:26" ht="247.5" x14ac:dyDescent="0.25">
       <c r="A36" s="1"/>
-      <c r="B36" s="11">
-        <v>10</v>
+      <c r="B36" s="19">
+        <v>9</v>
       </c>
-      <c r="C36" s="12" t="s">
-        <v>19</v>
+      <c r="C36" s="20" t="s">
+        <v>22</v>
       </c>
-      <c r="D36" s="13" t="s">
-        <v>87</v>
+      <c r="D36" s="21" t="s">
+        <v>84</v>
       </c>
-      <c r="E36" s="13" t="s">
-        <v>87</v>
+      <c r="E36" s="21" t="s">
+        <v>85</v>
       </c>
-      <c r="F36" s="4" t="s">
-        <v>88</v>
+      <c r="F36" s="21" t="s">
+        <v>86</v>
       </c>
-      <c r="G36" s="14"/>
+      <c r="G36" s="22"/>
       <c r="H36" s="1"/>
       <c r="I36" s="4"/>
       <c r="J36" s="4"/>
@@ -2580,24 +2623,24 @@
       <c r="Y36" s="4"/>
       <c r="Z36" s="4"/>
     </row>
-    <row r="37" spans="1:26" ht="115.5" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:26" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="1"/>
-      <c r="B37" s="31">
+      <c r="B37" s="11">
         <v>10</v>
       </c>
-      <c r="C37" s="32" t="s">
-        <v>22</v>
+      <c r="C37" s="12" t="s">
+        <v>19</v>
       </c>
-      <c r="D37" s="33" t="s">
-        <v>89</v>
+      <c r="D37" s="13" t="s">
+        <v>87</v>
       </c>
-      <c r="E37" s="33" t="s">
-        <v>90</v>
+      <c r="E37" s="13" t="s">
+        <v>87</v>
       </c>
-      <c r="F37" s="33" t="s">
-        <v>91</v>
+      <c r="F37" s="4" t="s">
+        <v>88</v>
       </c>
-      <c r="G37" s="27"/>
+      <c r="G37" s="14"/>
       <c r="H37" s="1"/>
       <c r="I37" s="4"/>
       <c r="J37" s="4"/>
@@ -2618,26 +2661,24 @@
       <c r="Y37" s="4"/>
       <c r="Z37" s="4"/>
     </row>
-    <row r="38" spans="1:26" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:26" ht="115.5" x14ac:dyDescent="0.25">
       <c r="A38" s="1"/>
-      <c r="B38" s="19">
+      <c r="B38" s="31">
         <v>10</v>
       </c>
-      <c r="C38" s="20" t="s">
-        <v>92</v>
+      <c r="C38" s="32" t="s">
+        <v>22</v>
       </c>
-      <c r="D38" s="28" t="s">
-        <v>93</v>
+      <c r="D38" s="33" t="s">
+        <v>89</v>
       </c>
-      <c r="E38" s="28" t="s">
-        <v>94</v>
+      <c r="E38" s="33" t="s">
+        <v>90</v>
       </c>
-      <c r="F38" s="28" t="s">
-        <v>95</v>
+      <c r="F38" s="33" t="s">
+        <v>91</v>
       </c>
-      <c r="G38" s="21" t="s">
-        <v>96</v>
-      </c>
+      <c r="G38" s="27"/>
       <c r="H38" s="1"/>
       <c r="I38" s="4"/>
       <c r="J38" s="4"/>
@@ -2660,12 +2701,24 @@
     </row>
     <row r="39" spans="1:26" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="1"/>
-      <c r="B39" s="2"/>
-      <c r="C39" s="2"/>
-      <c r="D39" s="3"/>
-      <c r="E39" s="3"/>
-      <c r="F39" s="3"/>
-      <c r="G39" s="1"/>
+      <c r="B39" s="19">
+        <v>10</v>
+      </c>
+      <c r="C39" s="20" t="s">
+        <v>92</v>
+      </c>
+      <c r="D39" s="28" t="s">
+        <v>93</v>
+      </c>
+      <c r="E39" s="28" t="s">
+        <v>94</v>
+      </c>
+      <c r="F39" s="28" t="s">
+        <v>95</v>
+      </c>
+      <c r="G39" s="21" t="s">
+        <v>96</v>
+      </c>
       <c r="H39" s="1"/>
       <c r="I39" s="4"/>
       <c r="J39" s="4"/>
@@ -2687,14 +2740,14 @@
       <c r="Z39" s="4"/>
     </row>
     <row r="40" spans="1:26" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="4"/>
-      <c r="B40" s="29"/>
-      <c r="C40" s="29"/>
-      <c r="D40" s="30"/>
-      <c r="E40" s="30"/>
-      <c r="F40" s="30"/>
-      <c r="G40" s="4"/>
-      <c r="H40" s="4"/>
+      <c r="A40" s="1"/>
+      <c r="B40" s="2"/>
+      <c r="C40" s="2"/>
+      <c r="D40" s="3"/>
+      <c r="E40" s="3"/>
+      <c r="F40" s="3"/>
+      <c r="G40" s="1"/>
+      <c r="H40" s="1"/>
       <c r="I40" s="4"/>
       <c r="J40" s="4"/>
       <c r="K40" s="4"/>
@@ -29593,6 +29646,34 @@
       <c r="X1000" s="4"/>
       <c r="Y1000" s="4"/>
       <c r="Z1000" s="4"/>
+    </row>
+    <row r="1001" spans="1:26" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1001" s="4"/>
+      <c r="B1001" s="29"/>
+      <c r="C1001" s="29"/>
+      <c r="D1001" s="30"/>
+      <c r="E1001" s="30"/>
+      <c r="F1001" s="30"/>
+      <c r="G1001" s="4"/>
+      <c r="H1001" s="4"/>
+      <c r="I1001" s="4"/>
+      <c r="J1001" s="4"/>
+      <c r="K1001" s="4"/>
+      <c r="L1001" s="4"/>
+      <c r="M1001" s="4"/>
+      <c r="N1001" s="4"/>
+      <c r="O1001" s="4"/>
+      <c r="P1001" s="4"/>
+      <c r="Q1001" s="4"/>
+      <c r="R1001" s="4"/>
+      <c r="S1001" s="4"/>
+      <c r="T1001" s="4"/>
+      <c r="U1001" s="4"/>
+      <c r="V1001" s="4"/>
+      <c r="W1001" s="4"/>
+      <c r="X1001" s="4"/>
+      <c r="Y1001" s="4"/>
+      <c r="Z1001" s="4"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2"/>
